--- a/_stats_outputs/erosion_totals.xlsx
+++ b/_stats_outputs/erosion_totals.xlsx
@@ -402,12 +402,12 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>tons_hectare</t>
+          <t>tons_km2</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>tons_hectare_se</t>
+          <t>tons_km2_se</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -456,10 +456,10 @@
         <v>0.005410543260007655</v>
       </c>
       <c r="J2">
-        <v>-72.23595934138439</v>
+        <v>-7223.595934138438</v>
       </c>
       <c r="K2">
-        <v>8.726212417588934</v>
+        <v>872.6212417588933</v>
       </c>
       <c r="L2">
         <v>-28.77122552579102</v>
@@ -503,10 +503,10 @@
         <v>0.005410543260007655</v>
       </c>
       <c r="J3">
-        <v>-53.6535571711298</v>
+        <v>-5365.355717112981</v>
       </c>
       <c r="K3">
-        <v>12.32990564991528</v>
+        <v>1232.990564991529</v>
       </c>
       <c r="L3">
         <v>-21.36994659870345</v>
@@ -550,16 +550,16 @@
         <v>0.008516172438153556</v>
       </c>
       <c r="J4">
-        <v>-20.06772827389367</v>
+        <v>-2006.772827389368</v>
       </c>
       <c r="K4">
-        <v>14.60677044640625</v>
+        <v>1460.677044640625</v>
       </c>
       <c r="L4">
-        <v>-7.992876971839531</v>
+        <v>-7.992876971839532</v>
       </c>
       <c r="M4">
-        <v>5.817804463991484</v>
+        <v>5.817804463991483</v>
       </c>
     </row>
     <row r="5">
@@ -597,10 +597,10 @@
         <v>0.008516172438153556</v>
       </c>
       <c r="J5">
-        <v>-25.14400687292163</v>
+        <v>-2514.400687292163</v>
       </c>
       <c r="K5">
-        <v>20.6562999934244</v>
+        <v>2065.62999934244</v>
       </c>
       <c r="L5">
         <v>-10.01473364455498</v>
@@ -644,10 +644,10 @@
         <v>0.008516172438153556</v>
       </c>
       <c r="J6">
-        <v>-50.66129482208483</v>
+        <v>-5066.129482208484</v>
       </c>
       <c r="K6">
-        <v>21.20476443488593</v>
+        <v>2120.476443488593</v>
       </c>
       <c r="L6">
         <v>-20.17814329655801</v>
@@ -691,10 +691,10 @@
         <v>0.008516172438153556</v>
       </c>
       <c r="J7">
-        <v>-20.84697402291413</v>
+        <v>-2084.697402291413</v>
       </c>
       <c r="K7">
-        <v>29.97324631206779</v>
+        <v>2997.324631206779</v>
       </c>
       <c r="L7">
         <v>-8.303246701673476</v>
@@ -738,16 +738,16 @@
         <v>0.005410543260007655</v>
       </c>
       <c r="J8">
-        <v>-72.30675907750708</v>
+        <v>-7230.675907750708</v>
       </c>
       <c r="K8">
-        <v>12.19376189450896</v>
+        <v>1219.376189450896</v>
       </c>
       <c r="L8">
         <v>-28.79942471070841</v>
       </c>
       <c r="M8">
-        <v>4.856715085857824</v>
+        <v>4.856715085857825</v>
       </c>
     </row>
     <row r="9">
@@ -785,16 +785,16 @@
         <v>0.005410543260007655</v>
       </c>
       <c r="J9">
-        <v>-64.90818665266495</v>
+        <v>-6490.818665266495</v>
       </c>
       <c r="K9">
-        <v>17.238186793512</v>
+        <v>1723.8186793512</v>
       </c>
       <c r="L9">
         <v>-25.8526098868333</v>
       </c>
       <c r="M9">
-        <v>6.865884587313922</v>
+        <v>6.865884587313921</v>
       </c>
     </row>
     <row r="10">
@@ -832,10 +832,10 @@
         <v>0.005410543260007655</v>
       </c>
       <c r="J10">
-        <v>-56.99378757892748</v>
+        <v>-5699.378757892748</v>
       </c>
       <c r="K10">
-        <v>14.33384460869744</v>
+        <v>1433.384460869743</v>
       </c>
       <c r="L10">
         <v>-22.70034385855951</v>
@@ -879,16 +879,16 @@
         <v>0.005410543260007655</v>
       </c>
       <c r="J11">
-        <v>-75.05024885226915</v>
+        <v>-7505.024885226915</v>
       </c>
       <c r="K11">
-        <v>20.27036449738724</v>
+        <v>2027.036449738725</v>
       </c>
       <c r="L11">
         <v>-29.8921431262602</v>
       </c>
       <c r="M11">
-        <v>8.073585977976977</v>
+        <v>8.073585977976979</v>
       </c>
     </row>
     <row r="12">
@@ -926,13 +926,13 @@
         <v>0.008516172438153556</v>
       </c>
       <c r="J12">
-        <v>-39.13430638017157</v>
+        <v>-3913.430638017157</v>
       </c>
       <c r="K12">
-        <v>6.433929447080954</v>
+        <v>643.3929447080956</v>
       </c>
       <c r="L12">
-        <v>-15.587000780846</v>
+        <v>-15.58700078084601</v>
       </c>
       <c r="M12">
         <v>2.562602294297244</v>
@@ -973,10 +973,10 @@
         <v>0.008516172438153556</v>
       </c>
       <c r="J13">
-        <v>-32.7489637303607</v>
+        <v>-3274.89637303607</v>
       </c>
       <c r="K13">
-        <v>9.078240987041442</v>
+        <v>907.8240987041441</v>
       </c>
       <c r="L13">
         <v>-13.0437503677251</v>

--- a/_stats_outputs/erosion_totals.xlsx
+++ b/_stats_outputs/erosion_totals.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -387,35 +387,45 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>estimate_mm</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>std_error_mm</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>worms</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>bd_mean</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>bd_se</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tons_km2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>tons_km2_se</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>tons_acre</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>tons_acre_se</t>
         </is>
@@ -436,36 +446,42 @@
         </is>
       </c>
       <c r="D2">
-        <v>-7.935555555555568</v>
+        <v>-2.972203031966552</v>
       </c>
       <c r="E2">
-        <v>0.9574659390385796</v>
+        <v>0.3580150973593705</v>
       </c>
       <c r="F2">
-        <v>6.570051489041413E-12</v>
-      </c>
-      <c r="G2" t="inlineStr">
+        <v>1.199350371471111E-14</v>
+      </c>
+      <c r="G2">
+        <v>-7.137198070182841</v>
+      </c>
+      <c r="H2">
+        <v>0.8597073061590147</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>EW</t>
         </is>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>0.9102823215800314</v>
       </c>
-      <c r="I2">
+      <c r="K2">
         <v>0.005410543260007655</v>
       </c>
-      <c r="J2">
-        <v>-7223.595934138438</v>
-      </c>
-      <c r="K2">
-        <v>872.6212417588933</v>
-      </c>
       <c r="L2">
-        <v>-28.77122552579102</v>
+        <v>-6496.865228902557</v>
       </c>
       <c r="M2">
-        <v>3.475607270139395</v>
+        <v>783.5285367044784</v>
+      </c>
+      <c r="N2">
+        <v>-25.87669305089941</v>
+      </c>
+      <c r="O2">
+        <v>3.120755429976344</v>
       </c>
     </row>
     <row r="3">
@@ -483,36 +499,42 @@
         </is>
       </c>
       <c r="D3">
-        <v>-5.89416666666668</v>
+        <v>0.5497091268668365</v>
       </c>
       <c r="E3">
-        <v>1.354061316498649</v>
+        <v>0.5063098062199471</v>
       </c>
       <c r="F3">
-        <v>0.136287873254571</v>
-      </c>
-      <c r="G3" t="inlineStr">
+        <v>0.2023586365478415</v>
+      </c>
+      <c r="G3">
+        <v>1.320025205963127</v>
+      </c>
+      <c r="H3">
+        <v>1.215809732041321</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>EW</t>
         </is>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>0.9102823215800314</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>0.005410543260007655</v>
       </c>
-      <c r="J3">
-        <v>-5365.355717112981</v>
-      </c>
-      <c r="K3">
-        <v>1232.990564991529</v>
-      </c>
       <c r="L3">
-        <v>-21.36994659870345</v>
+        <v>1201.595609028274</v>
       </c>
       <c r="M3">
-        <v>4.910940470644533</v>
+        <v>1106.753150123595</v>
+      </c>
+      <c r="N3">
+        <v>4.785895912971776</v>
+      </c>
+      <c r="O3">
+        <v>4.408143087447414</v>
       </c>
     </row>
     <row r="4">
@@ -530,36 +552,42 @@
         </is>
       </c>
       <c r="D4">
-        <v>-3.240555555555557</v>
+        <v>-1.054667005822169</v>
       </c>
       <c r="E4">
-        <v>2.358293950359017</v>
+        <v>0.6897618556613508</v>
       </c>
       <c r="F4">
-        <v>0.173919917785566</v>
-      </c>
-      <c r="G4" t="inlineStr">
+        <v>0.1277475365557665</v>
+      </c>
+      <c r="G4">
+        <v>-2.532588533717708</v>
+      </c>
+      <c r="H4">
+        <v>1.65633603497627</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>JW</t>
         </is>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>0.6192681449169999</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>0.008516172438153556</v>
       </c>
-      <c r="J4">
-        <v>-2006.772827389368</v>
-      </c>
-      <c r="K4">
-        <v>1460.677044640625</v>
-      </c>
       <c r="L4">
-        <v>-7.992876971839532</v>
+        <v>-1568.35140311343</v>
       </c>
       <c r="M4">
-        <v>5.817804463991483</v>
+        <v>1025.942875824013</v>
+      </c>
+      <c r="N4">
+        <v>-6.246666111183745</v>
+      </c>
+      <c r="O4">
+        <v>4.086279759560206</v>
       </c>
     </row>
     <row r="5">
@@ -577,36 +605,42 @@
         </is>
       </c>
       <c r="D5">
-        <v>-4.060277777777778</v>
+        <v>-0.2919915069809507</v>
       </c>
       <c r="E5">
-        <v>3.335131288660141</v>
+        <v>0.9754705710839164</v>
       </c>
       <c r="F5">
-        <v>0.8065897105332439</v>
-      </c>
-      <c r="G5" t="inlineStr">
+        <v>0.7922144381015715</v>
+      </c>
+      <c r="G5">
+        <v>-0.7011638161055723</v>
+      </c>
+      <c r="H5">
+        <v>2.342412884510721</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>JW</t>
         </is>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>0.6192681449169999</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>0.008516172438153556</v>
       </c>
-      <c r="J5">
-        <v>-2514.400687292163</v>
-      </c>
-      <c r="K5">
-        <v>2065.62999934244</v>
-      </c>
       <c r="L5">
-        <v>-10.01473364455498</v>
+        <v>-434.2084156826222</v>
       </c>
       <c r="M5">
-        <v>8.227302178275734</v>
+        <v>1450.593971676612</v>
+      </c>
+      <c r="N5">
+        <v>-1.729430655687852</v>
+      </c>
+      <c r="O5">
+        <v>5.777644082806592</v>
       </c>
     </row>
     <row r="6">
@@ -624,36 +658,42 @@
         </is>
       </c>
       <c r="D6">
-        <v>-8.180833333333323</v>
+        <v>-3.704461401319306</v>
       </c>
       <c r="E6">
-        <v>3.422316551173235</v>
+        <v>1.049240775682377</v>
       </c>
       <c r="F6">
-        <v>0.01960380934699692</v>
-      </c>
-      <c r="G6" t="inlineStr">
+        <v>0.0005085328977981283</v>
+      </c>
+      <c r="G6">
+        <v>-8.530009805669456</v>
+      </c>
+      <c r="H6">
+        <v>2.416014944005473</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>JW</t>
         </is>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>0.6192681449169999</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <v>0.008516172438153556</v>
       </c>
-      <c r="J6">
-        <v>-5066.129482208484</v>
-      </c>
-      <c r="K6">
-        <v>2120.476443488593</v>
-      </c>
       <c r="L6">
-        <v>-20.17814329655801</v>
+        <v>-5282.363348480743</v>
       </c>
       <c r="M6">
-        <v>8.445752854116988</v>
+        <v>1497.923571166621</v>
+      </c>
+      <c r="N6">
+        <v>-21.03939209695549</v>
+      </c>
+      <c r="O6">
+        <v>5.966155537958304</v>
       </c>
     </row>
     <row r="7">
@@ -671,36 +711,42 @@
         </is>
       </c>
       <c r="D7">
-        <v>-3.366388888888873</v>
+        <v>1.573218527762946</v>
       </c>
       <c r="E7">
-        <v>4.83988648140311</v>
+        <v>1.483850535164893</v>
       </c>
       <c r="F7">
-        <v>0.3233877886534533</v>
-      </c>
-      <c r="G7" t="inlineStr">
+        <v>0.2545973202353868</v>
+      </c>
+      <c r="G7">
+        <v>3.622542662612047</v>
+      </c>
+      <c r="H7">
+        <v>3.416761100708636</v>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>JW</t>
         </is>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>0.6192681449169999</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>0.008516172438153556</v>
       </c>
-      <c r="J7">
-        <v>-2084.697402291413</v>
-      </c>
-      <c r="K7">
-        <v>2997.324631206779</v>
-      </c>
       <c r="L7">
-        <v>-8.303246701673476</v>
+        <v>2243.325274558452</v>
       </c>
       <c r="M7">
-        <v>11.93819584106405</v>
+        <v>2116.116198117118</v>
+      </c>
+      <c r="N7">
+        <v>8.935053675552297</v>
+      </c>
+      <c r="O7">
+        <v>8.428386212339914</v>
       </c>
     </row>
     <row r="8">
@@ -718,36 +764,42 @@
         </is>
       </c>
       <c r="D8">
-        <v>-7.943333333333324</v>
+        <v>-3.685901184817794</v>
       </c>
       <c r="E8">
-        <v>1.338725948103235</v>
+        <v>0.5220469905099397</v>
       </c>
       <c r="F8">
-        <v>1.110786983330941E-07</v>
-      </c>
-      <c r="G8" t="inlineStr">
+        <v>2.334409443926573E-11</v>
+      </c>
+      <c r="G8">
+        <v>-9.335999711545071</v>
+      </c>
+      <c r="H8">
+        <v>1.322290074646887</v>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>EW</t>
         </is>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>0.9102823215800314</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>0.005410543260007655</v>
       </c>
-      <c r="J8">
-        <v>-7230.675907750708</v>
-      </c>
-      <c r="K8">
-        <v>1219.376189450896</v>
-      </c>
       <c r="L8">
-        <v>-28.79942471070841</v>
+        <v>-8498.39549169575</v>
       </c>
       <c r="M8">
-        <v>4.856715085857825</v>
+        <v>1204.716726537844</v>
+      </c>
+      <c r="N8">
+        <v>-33.84868914710508</v>
+      </c>
+      <c r="O8">
+        <v>4.798327169727978</v>
       </c>
     </row>
     <row r="9">
@@ -765,36 +817,42 @@
         </is>
       </c>
       <c r="D9">
-        <v>-7.130555555555548</v>
+        <v>0.3546779250189292</v>
       </c>
       <c r="E9">
-        <v>1.893244392108377</v>
+        <v>0.7382859341752143</v>
       </c>
       <c r="F9">
-        <v>0.6690590271085073</v>
-      </c>
-      <c r="G9" t="inlineStr">
+        <v>0.5198609087920016</v>
+      </c>
+      <c r="G9">
+        <v>0.8983618495545247</v>
+      </c>
+      <c r="H9">
+        <v>1.870000556956957</v>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>EW</t>
         </is>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>0.9102823215800314</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>0.005410543260007655</v>
       </c>
-      <c r="J9">
-        <v>-6490.818665266495</v>
-      </c>
-      <c r="K9">
-        <v>1723.8186793512</v>
-      </c>
       <c r="L9">
-        <v>-25.8526098868333</v>
+        <v>817.7629100314236</v>
       </c>
       <c r="M9">
-        <v>6.865884587313921</v>
+        <v>1702.235387961668</v>
+      </c>
+      <c r="N9">
+        <v>3.25710924664939</v>
+      </c>
+      <c r="O9">
+        <v>6.779919404623906</v>
       </c>
     </row>
     <row r="10">
@@ -812,36 +870,42 @@
         </is>
       </c>
       <c r="D10">
-        <v>-6.261111111111106</v>
+        <v>-1.962696597093065</v>
       </c>
       <c r="E10">
-        <v>1.574219409941141</v>
+        <v>0.4877951197862384</v>
       </c>
       <c r="F10">
-        <v>0.0001715313002135744</v>
-      </c>
-      <c r="G10" t="inlineStr">
+        <v>7.973704403488446E-05</v>
+      </c>
+      <c r="G10">
+        <v>-4.971303880794934</v>
+      </c>
+      <c r="H10">
+        <v>1.235533691563828</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>EW</t>
         </is>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>0.9102823215800314</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>0.005410543260007655</v>
       </c>
-      <c r="J10">
-        <v>-5699.378757892748</v>
-      </c>
-      <c r="K10">
-        <v>1433.384460869743</v>
-      </c>
       <c r="L10">
-        <v>-22.70034385855951</v>
+        <v>-4525.290037889832</v>
       </c>
       <c r="M10">
-        <v>5.709099451970732</v>
+        <v>1125.006064963748</v>
+      </c>
+      <c r="N10">
+        <v>-18.02400652484344</v>
+      </c>
+      <c r="O10">
+        <v>4.480843544969853</v>
       </c>
     </row>
     <row r="11">
@@ -859,36 +923,42 @@
         </is>
       </c>
       <c r="D11">
-        <v>-8.244722222222217</v>
+        <v>-0.8717593984638676</v>
       </c>
       <c r="E11">
-        <v>2.226282439689734</v>
+        <v>0.6898464740611059</v>
       </c>
       <c r="F11">
-        <v>0.3760725424731571</v>
-      </c>
-      <c r="G11" t="inlineStr">
+        <v>0.243269994461641</v>
+      </c>
+      <c r="G11">
+        <v>-2.20807479216177</v>
+      </c>
+      <c r="H11">
+        <v>1.747308503378459</v>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>EW</t>
         </is>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>0.9102823215800314</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>0.005410543260007655</v>
       </c>
-      <c r="J11">
-        <v>-7505.024885226915</v>
-      </c>
-      <c r="K11">
-        <v>2027.036449738725</v>
-      </c>
       <c r="L11">
-        <v>-29.8921431262602</v>
+        <v>-2009.971448031362</v>
       </c>
       <c r="M11">
-        <v>8.073585977976979</v>
+        <v>1590.58890801893</v>
+      </c>
+      <c r="N11">
+        <v>-8.00561691974101</v>
+      </c>
+      <c r="O11">
+        <v>6.335236993968504</v>
       </c>
     </row>
     <row r="12">
@@ -906,36 +976,42 @@
         </is>
       </c>
       <c r="D12">
-        <v>-6.319444444444452</v>
+        <v>-3.513983734987653</v>
       </c>
       <c r="E12">
-        <v>1.035315930472249</v>
+        <v>0.5045130976286406</v>
       </c>
       <c r="F12">
-        <v>5.593000530393844E-08</v>
-      </c>
-      <c r="G12" t="inlineStr">
+        <v>4.060148226100291E-11</v>
+      </c>
+      <c r="G12">
+        <v>-7.975818345860135</v>
+      </c>
+      <c r="H12">
+        <v>1.145111965012375</v>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>JW</t>
         </is>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>0.6192681449169999</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>0.008516172438153556</v>
       </c>
-      <c r="J12">
-        <v>-3913.430638017157</v>
-      </c>
-      <c r="K12">
-        <v>643.3929447080956</v>
-      </c>
       <c r="L12">
-        <v>-15.58700078084601</v>
+        <v>-4939.17023123578</v>
       </c>
       <c r="M12">
-        <v>2.562602294297244</v>
+        <v>712.3769250094695</v>
+      </c>
+      <c r="N12">
+        <v>-19.6724708758377</v>
+      </c>
+      <c r="O12">
+        <v>2.837362077792012</v>
       </c>
     </row>
     <row r="13">
@@ -953,36 +1029,42 @@
         </is>
       </c>
       <c r="D13">
-        <v>-5.288333333333337</v>
+        <v>0.2414075946472465</v>
       </c>
       <c r="E13">
-        <v>1.464157830214773</v>
+        <v>0.7134892650612854</v>
       </c>
       <c r="F13">
-        <v>0.4836913027115114</v>
-      </c>
-      <c r="G13" t="inlineStr">
+        <v>0.6173429156469129</v>
+      </c>
+      <c r="G13">
+        <v>0.5479317115348686</v>
+      </c>
+      <c r="H13">
+        <v>1.619432871356207</v>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>JW</t>
         </is>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>0.6192681449169999</v>
       </c>
-      <c r="I13">
+      <c r="K13">
         <v>0.008516172438153556</v>
       </c>
-      <c r="J13">
-        <v>-3274.89637303607</v>
-      </c>
-      <c r="K13">
-        <v>907.8240987041441</v>
-      </c>
       <c r="L13">
-        <v>-13.0437503677251</v>
+        <v>339.3166545433948</v>
       </c>
       <c r="M13">
-        <v>3.615818509189655</v>
+        <v>1002.874046009707</v>
+      </c>
+      <c r="N13">
+        <v>1.351481461800413</v>
+      </c>
+      <c r="O13">
+        <v>3.994397750758081</v>
       </c>
     </row>
   </sheetData>
